--- a/PySpark/PySparkNotes.xlsx
+++ b/PySpark/PySparkNotes.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C813BFE0-428A-487D-AC0E-045F1DF703D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D52CCDB1-9BAB-4A68-9D64-250C18B69269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="DataCamp" sheetId="3" r:id="rId3"/>
     <sheet name="SibramNanda" sheetId="4" r:id="rId4"/>
     <sheet name="AminKarami" sheetId="5" r:id="rId5"/>
+    <sheet name="kindle-DefinitiveGuide" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="438">
   <si>
     <t>Why Spark</t>
   </si>
@@ -1440,7 +1441,114 @@
     <t>rddJson.map(lambda x: [datefn(x['update_date']),1]).reduceByKey(lambda x,y: x+y).collect()  # datefn returns month, then a group of maonth and 1 is created. Then reduceByKKey and here x,y will be both 1s of that month</t>
   </si>
   <si>
-    <t>jsonDF</t>
+    <t>RDD DF</t>
+  </si>
+  <si>
+    <t>rdd1.persist(storageLevel= StorageLevel.MEMORY_AND_DISK)</t>
+  </si>
+  <si>
+    <t>rdd1.takeSample(False,2)</t>
+  </si>
+  <si>
+    <t>rddFinal.take(3)</t>
+  </si>
+  <si>
+    <t>rdd1.filter(lambda x: 'WARN' in  x.split(',')[0]).collect()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spark </t>
+  </si>
+  <si>
+    <t>A unified compute engine and set of libraries  for running parallel processing on a cluster</t>
+  </si>
+  <si>
+    <t>To alow each executor to work in parallel, spark breakes the data in chunks called partitions</t>
+  </si>
+  <si>
+    <t>A partition is a collection of rows that sit on one computer in clusted</t>
+  </si>
+  <si>
+    <t>If you have one partions then there is no parallelism even if there are many hundred workers</t>
+  </si>
+  <si>
+    <t>Transformation: This is the data processing logic that we need to perform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrow Transformation are 1-to-1 </t>
+  </si>
+  <si>
+    <t>shuffle: Wide transformation , where input partitions contribute to many output partitions</t>
+  </si>
+  <si>
+    <t>In shuffle, spark exchanges partions across cluster</t>
+  </si>
+  <si>
+    <t>with Narrow, spark automatically performs an operation called pipelining , which means calculation will be in memory</t>
+  </si>
+  <si>
+    <t>for wide transformation this may not be prossible as large output may be required to be written on disk</t>
+  </si>
+  <si>
+    <t>lazy</t>
+  </si>
+  <si>
+    <t>The code is not executed till last moment.</t>
+  </si>
+  <si>
+    <t>spark builds a transformation plan first and compiles plan with raw data and created an optimized plan</t>
+  </si>
+  <si>
+    <t>action</t>
+  </si>
+  <si>
+    <t>It triggers the calculation</t>
+  </si>
+  <si>
+    <t>A sql query against a DF creates a new DF. This is very powerful concept</t>
+  </si>
+  <si>
+    <t>dataframeName.groupBy('col1).count()        The will give same explain plan as  "select col1, count(1) from dataframeNameTempView"</t>
+  </si>
+  <si>
+    <t>Spart ToolSets</t>
+  </si>
+  <si>
+    <t>Low Level APIs
+RDDs and Distributed variables</t>
+  </si>
+  <si>
+    <t>Structured API
+dataFrame, SQL, dataset</t>
+  </si>
+  <si>
+    <t>streaming</t>
+  </si>
+  <si>
+    <t>libraries</t>
+  </si>
+  <si>
+    <t>advace analytics</t>
+  </si>
+  <si>
+    <t>Structured API Overview</t>
+  </si>
+  <si>
+    <t>structured apis apply both batch and streaming computations</t>
+  </si>
+  <si>
+    <t>structured apis are funcdamental abstractions to write code</t>
+  </si>
+  <si>
+    <t>untyped api</t>
+  </si>
+  <si>
+    <t>typed api</t>
+  </si>
+  <si>
+    <t>how spark takes structed api and excutes on cluster</t>
+  </si>
+  <si>
+    <t>Dataframe</t>
   </si>
 </sst>
 </file>
@@ -1511,7 +1619,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1519,11 +1627,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1532,6 +1655,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3088,7 +3218,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F2FE25F-722F-49F6-9D5D-8AAD0C7A88D7}">
-  <dimension ref="A2:D240"/>
+  <dimension ref="A2:D245"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="2" spans="1:2" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -4225,8 +4355,212 @@
         <v>402</v>
       </c>
     </row>
+    <row r="241" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D241" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="242" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D242" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="243" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D243" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="244" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D244" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="245" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D245" t="s">
+        <v>406</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBC370A0-3FFD-43D7-BC08-4302B41993E9}">
+  <dimension ref="A1:J39"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C9" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C10" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C11" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C13" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C14" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C16" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C19" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B23">
+        <v>3</v>
+      </c>
+      <c r="C23" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="F25" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="G25" t="s">
+        <v>429</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="F26" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+    </row>
+    <row r="27" spans="2:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F27" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B32">
+        <v>4</v>
+      </c>
+      <c r="C32" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C33" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C34" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="35" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="D35" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="36" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="D36" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="37" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="D37" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="39" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C39" t="s">
+        <v>437</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="F27:J27"/>
+    <mergeCell ref="F26:J26"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>